--- a/Result/profitability/2404.xlsx
+++ b/Result/profitability/2404.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.36</v>
       </c>
       <c r="M2" t="n">
-        <v>10.565</v>
+        <v>11.8975</v>
       </c>
       <c r="N2" t="n">
-        <v>20.7925</v>
+        <v>20.56375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>9.469999999999999</v>
+        <v>10.6475</v>
       </c>
       <c r="N3" t="n">
-        <v>19.07</v>
+        <v>19.44125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>8.234999999999999</v>
+        <v>9.40625</v>
       </c>
       <c r="N4" t="n">
-        <v>18.0525</v>
+        <v>18.10625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>6.954999999999999</v>
+        <v>8.518750000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>16.315</v>
+        <v>16.6125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>6.069999999999999</v>
+        <v>6.54625</v>
       </c>
       <c r="N6" t="n">
-        <v>15.44625</v>
+        <v>15.87875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.28</v>
       </c>
       <c r="M7" t="n">
-        <v>4.09125</v>
+        <v>4.828749999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>16.6725</v>
+        <v>17.47875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.41</v>
       </c>
       <c r="M8" t="n">
-        <v>2.39</v>
+        <v>2.84125</v>
       </c>
       <c r="N8" t="n">
-        <v>17.29375</v>
+        <v>17.33375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>26080</v>
+      </c>
+      <c r="D75" t="n">
+        <v>19916</v>
+      </c>
+      <c r="E75" t="n">
+        <v>6165</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5205</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>19.96%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>421</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5626</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3763</v>
+      </c>
+      <c r="L75" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="M75" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.8675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.610000000000003</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2213366033108524</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.3200000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01372212692967412</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.688259109311741</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.379999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1119473189087488</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
